--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.247</t>
+    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">new</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">New Items</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Category.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="566">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -601,6 +601,21 @@
     <t xml:space="preserve">実</t>
   </si>
   <si>
+    <t xml:space="preserve">filling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필링</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィリング</t>
+  </si>
+  <si>
     <t xml:space="preserve">seasoning</t>
   </si>
   <si>
@@ -727,7 +742,7 @@
     <t xml:space="preserve">밀크</t>
   </si>
   <si>
-    <t xml:space="preserve">Milk</t>
+    <t xml:space="preserve">Dairy</t>
   </si>
   <si>
     <t xml:space="preserve">ミルク</t>
@@ -1934,7 +1949,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="16.15"/>
@@ -2744,50 +2759,50 @@
         <v>192</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>6</v>
+        <v>193</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B51" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="C51" s="0" t="s">
+      <c r="D51" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="D51" s="0" t="s">
+      <c r="E51" s="0" t="s">
         <v>200</v>
-      </c>
-      <c r="E51" s="0" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2795,92 +2810,92 @@
         <v>202</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B53" s="0" t="s">
         <v>176</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B55" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B56" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>223</v>
+        <v>6</v>
       </c>
       <c r="C57" s="0" t="s">
         <v>224</v>
@@ -2897,24 +2912,24 @@
         <v>227</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>6</v>
+        <v>228</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>232</v>
+        <v>6</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>233</v>
@@ -2931,279 +2946,279 @@
         <v>236</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>6</v>
+        <v>237</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B61" s="0" t="s">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B62" s="0" t="s">
         <v>100</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B64" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B65" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B66" s="0" t="s">
-        <v>176</v>
+        <v>6</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E66" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B68" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B69" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>198</v>
+        <v>6</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>6</v>
+        <v>203</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E72" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B73" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B74" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E74" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E75" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>301</v>
+        <v>6</v>
       </c>
       <c r="C76" s="0" t="s">
         <v>302</v>
@@ -3237,279 +3252,279 @@
         <v>310</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>6</v>
+        <v>311</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E79" s="0" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B80" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B81" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B83" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B84" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E84" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B85" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B86" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B87" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B88" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E88" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B89" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B90" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B91" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B92" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E92" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B94" s="0" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C94" s="0" t="s">
         <v>372</v>
@@ -3523,129 +3538,129 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B95" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B96" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B97" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E98" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B99" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B100" s="0" t="s">
-        <v>176</v>
+        <v>6</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E100" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>176</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B102" s="0" t="s">
-        <v>404</v>
+        <v>176</v>
       </c>
       <c r="C102" s="0" t="s">
         <v>405</v>
@@ -3662,58 +3677,58 @@
         <v>408</v>
       </c>
       <c r="B103" s="0" t="s">
-        <v>6</v>
+        <v>409</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B104" s="0" t="s">
-        <v>404</v>
+        <v>6</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E104" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B105" s="0" t="s">
-        <v>6</v>
+        <v>409</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E105" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B106" s="0" t="s">
-        <v>421</v>
+        <v>6</v>
       </c>
       <c r="C106" s="0" t="s">
         <v>422</v>
@@ -3730,92 +3745,92 @@
         <v>425</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>6</v>
+        <v>426</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B108" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B109" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B111" s="0" t="s">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E111" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B112" s="0" t="s">
-        <v>446</v>
+        <v>87</v>
       </c>
       <c r="C112" s="0" t="s">
         <v>447</v>
@@ -3832,50 +3847,50 @@
         <v>450</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>6</v>
+        <v>451</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E113" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B114" s="0" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E114" s="0" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B115" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="C115" s="0" t="s">
+      <c r="D115" s="0" t="s">
         <v>457</v>
       </c>
-      <c r="D115" s="0" t="s">
+      <c r="E115" s="0" t="s">
         <v>458</v>
-      </c>
-      <c r="E115" s="0" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3883,75 +3898,75 @@
         <v>460</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E116" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B117" s="0" t="s">
-        <v>52</v>
+        <v>461</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B118" s="0" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B120" s="0" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C120" s="0" t="s">
         <v>474</v>
@@ -3965,78 +3980,78 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B121" s="0" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E121" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B122" s="0" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B123" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E123" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B124" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E124" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B125" s="0" t="s">
-        <v>494</v>
+        <v>6</v>
       </c>
       <c r="C125" s="0" t="s">
         <v>495</v>
@@ -4053,211 +4068,211 @@
         <v>498</v>
       </c>
       <c r="B126" s="0" t="s">
-        <v>6</v>
+        <v>499</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B127" s="0" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B128" s="0" t="s">
         <v>52</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B129" s="0" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E129" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B130" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E130" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B131" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B132" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B133" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E133" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B134" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>446</v>
+        <v>6</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>6</v>
+        <v>451</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E136" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="E137" s="0" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B138" s="0" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C138" s="0" t="s">
         <v>544</v>
@@ -4271,10 +4286,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B139" s="0" t="s">
-        <v>548</v>
+        <v>6</v>
       </c>
       <c r="C139" s="0" t="s">
         <v>549</v>
@@ -4308,16 +4323,33 @@
         <v>557</v>
       </c>
       <c r="B141" s="0" t="s">
-        <v>6</v>
+        <v>558</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="B142" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="D142" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
